--- a/erp-server/erp-server-tms/src/main/resources/excel/shippingTemplateError_country2.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/shippingTemplateError_country2.xlsx
@@ -8,15 +8,13 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
   <si>
     <r>
       <rPr>
@@ -301,6 +299,69 @@
   </si>
   <si>
     <t>保险费</t>
+  </si>
+  <si>
+    <t>错误信息</t>
+  </si>
+  <si>
+    <t>{.name}</t>
+  </si>
+  <si>
+    <t>{.currency}</t>
+  </si>
+  <si>
+    <t>{.weightUnit}</t>
+  </si>
+  <si>
+    <t>{.priceBinary}</t>
+  </si>
+  <si>
+    <t>{.volumeSetting}</t>
+  </si>
+  <si>
+    <t>{.effectiveDate}</t>
+  </si>
+  <si>
+    <t>{.expireDate}</t>
+  </si>
+  <si>
+    <t>{.fromCountry}</t>
+  </si>
+  <si>
+    <t>{.toCountry}</t>
+  </si>
+  <si>
+    <t>{.startWeight}</t>
+  </si>
+  <si>
+    <t>{.endWeight}</t>
+  </si>
+  <si>
+    <t>{.shippingPrice}</t>
+  </si>
+  <si>
+    <t>{.registrationCost}</t>
+  </si>
+  <si>
+    <t>{.operatingCost}</t>
+  </si>
+  <si>
+    <t>{.minCost}</t>
+  </si>
+  <si>
+    <t>{.discountRate}</t>
+  </si>
+  <si>
+    <t>{.signatureCost}</t>
+  </si>
+  <si>
+    <t>{.fuelSurchargeRate}</t>
+  </si>
+  <si>
+    <t>{.premiumCost}</t>
+  </si>
+  <si>
+    <t>{.errorMsg}</t>
   </si>
 </sst>
 </file>
@@ -1278,7 +1339,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S2"/>
+  <dimension ref="A1:T2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="20.875" customWidth="1"/>
@@ -1293,13 +1354,14 @@
     <col min="11" max="11" width="13.375" customWidth="1"/>
     <col min="12" max="12" width="10.875" customWidth="1"/>
     <col min="13" max="13" width="10.75" customWidth="1"/>
-    <col min="14" max="14" width="10.625" customWidth="1"/>
-    <col min="15" max="15" width="11.375" customWidth="1"/>
+    <col min="14" max="14" width="17.75" customWidth="1"/>
+    <col min="15" max="15" width="18.625" customWidth="1"/>
     <col min="16" max="16" width="11.875" customWidth="1"/>
     <col min="18" max="18" width="14.5" customWidth="1"/>
+    <col min="20" max="20" width="21.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="20.25" customHeight="1" spans="1:19">
+    <row r="1" s="1" customFormat="1" ht="20.25" customHeight="1" spans="1:20">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1357,50 +1419,75 @@
       <c r="S1" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
     </row>
-    <row r="2" spans="6:6">
-      <c r="F2" s="3"/>
+    <row r="2" spans="1:20">
+      <c r="A2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J2" t="s">
+        <v>29</v>
+      </c>
+      <c r="K2" t="s">
+        <v>30</v>
+      </c>
+      <c r="L2" t="s">
+        <v>31</v>
+      </c>
+      <c r="M2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O2" t="s">
+        <v>34</v>
+      </c>
+      <c r="P2" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>36</v>
+      </c>
+      <c r="R2" t="s">
+        <v>37</v>
+      </c>
+      <c r="S2" t="s">
+        <v>38</v>
+      </c>
+      <c r="T2" t="s">
+        <v>39</v>
+      </c>
     </row>
   </sheetData>
-  <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B$1:B$1048576">
-      <formula1>"CNY,JPY,GBP,CAD,USD,EUR,KRW,AUD"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C$1:C$1048576">
-      <formula1>"kg,g"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D$1:D$1048576">
-      <formula1>"0.01  保留两位小数四金五入,0.1  保留一位小数四舍五入,0  向下取整，小数舍弃,0.5  0.5进制,1  向上取整，小数进1,2  保留整数，四舍五入"</formula1>
-    </dataValidation>
-    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F$1:F$1048576 G$1:G$1048576">
-      <formula1>32874</formula1>
-      <formula2>398117</formula2>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
-</worksheet>
 </file>
--- a/erp-server/erp-server-tms/src/main/resources/excel/shippingTemplateError_country2.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/shippingTemplateError_country2.xlsx
@@ -148,26 +148,7 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>失效日期</t>
-    </r>
+    <t>失效日期</t>
   </si>
   <si>
     <r>
@@ -982,12 +963,15 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1380,7 +1364,7 @@
       <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="2" t="s">
@@ -1439,7 +1423,7 @@
       <c r="E2" t="s">
         <v>24</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="4" t="s">
         <v>25</v>
       </c>
       <c r="G2" t="s">
